--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/sep-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1006,7 +1022,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4858-804-CM26</t>
+          <t>585-115-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1031,43 +1047,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>34871.35</v>
+        <v>25127.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>585-115-CM26</t>
+          <t>585-114-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1115,20 +1135,24 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>25127.36</v>
+        <v>26219.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>585-114-CM26</t>
+          <t>585-113-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1176,14 +1200,18 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26219.86</v>
+        <v>25127.36</v>
       </c>
     </row>
     <row r="13">
@@ -1254,7 +1282,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4168-1233-CM26</t>
+          <t>5158-111-SE26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1274,48 +1302,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>53039.13</v>
+        <v>87066.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>585-113-CM26</t>
+          <t>4168-1233-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1340,43 +1372,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>H. Motores S.A.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>25127.36</v>
+        <v>53039.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5240-192-CM26</t>
+          <t>4858-804-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1391,7 +1427,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1401,32 +1437,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1435,13 +1471,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>61547.18</v>
+        <v>34871.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4168-1234-CM26</t>
+          <t>5158-112-SE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1456,7 +1492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1466,43 +1502,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1924.22</v>
+        <v>29663.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4858-828-CM26</t>
+          <t>4168-1234-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1517,7 +1557,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1527,43 +1567,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>34742.03</v>
+        <v>1924.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3866-125-CM26</t>
+          <t>5240-192-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1578,7 +1622,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,37 +1632,41 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1381.53</v>
+        <v>61547.18</v>
       </c>
     </row>
     <row r="20">
@@ -1733,7 +1781,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1746,7 +1798,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1223542-174-CM26</t>
+          <t>3866-125-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1761,7 +1813,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1771,43 +1823,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.104.928-8</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13638.66</v>
+        <v>1381.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1223542-175-CM26</t>
+          <t>4858-828-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,7 +1878,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,43 +1888,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.104.928-8</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>197.3</v>
+        <v>34742.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4036-374-CM26</t>
+          <t>1223542-174-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1893,43 +1953,47 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.050.575-5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>50760.61</v>
+        <v>13638.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2859-1011-CM26</t>
+          <t>1223542-175-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1954,43 +2018,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.050.575-5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>71710.75</v>
+        <v>197.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>651-153-CM26</t>
+          <t>4036-374-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2005,7 +2073,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2015,27 +2083,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2045,13 +2113,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>29827.14</v>
+        <v>50760.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>651-154-CM26</t>
+          <t>2859-1011-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2134,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2076,12 +2144,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,12 +2159,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2106,13 +2174,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>435.68</v>
+        <v>71710.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>642-179-CM26</t>
+          <t>651-153-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2137,43 +2205,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.818.000-K</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>61013.48</v>
+        <v>29827.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5612-180-CM26</t>
+          <t>651-154-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2198,43 +2270,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>39756.82</v>
+        <v>435.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5413-979-CM26</t>
+          <t>642-179-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2259,43 +2335,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.818.000-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>32671.57</v>
+        <v>61013.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2432-632-CM26</t>
+          <t>5612-180-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2310,7 +2390,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2320,43 +2400,47 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17061.25</v>
+        <v>39756.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4803-226-CM26</t>
+          <t>5413-979-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2371,7 +2455,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2381,43 +2465,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36732.47</v>
+        <v>32671.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29-1907-CM26</t>
+          <t>2432-632-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2432,7 +2520,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2442,12 +2530,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2457,28 +2545,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>58176.41</v>
+        <v>17061.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4803-227-CM26</t>
+          <t>4803-226-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2526,20 +2618,24 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>931.28</v>
+        <v>36732.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2458-270-CM26</t>
+          <t>4803-227-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2554,7 +2650,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2564,43 +2660,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>22017.08</v>
+        <v>931.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2345-480-CM26</t>
+          <t>29-1907-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2615,7 +2715,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2625,12 +2725,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2640,28 +2740,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>61963.39</v>
+        <v>58176.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4371-408-CM26</t>
+          <t>2458-270-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2676,7 +2780,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2686,43 +2790,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PORTILLO S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.008.670-1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>34485.94</v>
+        <v>22017.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4371-409-CM26</t>
+          <t>2345-480-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2747,43 +2855,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PORTILLO S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.008.670-1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>217.61</v>
+        <v>61963.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1546284-2-CM26</t>
+          <t>4371-408-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2798,7 +2910,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2808,27 +2920,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>PORTILLO S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>77.008.670-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2838,13 +2950,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>74856.99000000001</v>
+        <v>34485.94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1483311-6-CM26</t>
+          <t>4371-409-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2859,7 +2971,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2869,27 +2981,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>PORTILLO S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>77.008.670-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2899,13 +3011,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>24520.12</v>
+        <v>217.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1483311-7-CM26</t>
+          <t>1546284-2-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2930,43 +3042,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1032.44</v>
+        <v>74856.99000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>756-289-CM26</t>
+          <t>1483311-6-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2991,12 +3107,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,28 +3122,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DERCO S.P.A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>94.141.000-6</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>38751.05</v>
+        <v>24520.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>756-290-CM26</t>
+          <t>1483311-7-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3052,12 +3172,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,28 +3187,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DERCO S.P.A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>94.141.000-6</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1235.95</v>
+        <v>1032.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2548-545-CM26</t>
+          <t>756-289-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3103,7 +3227,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3113,27 +3237,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>DERCO S.P.A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>94.141.000-6</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3143,13 +3267,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>44008.37</v>
+        <v>38751.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4486-282-CM26</t>
+          <t>756-290-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,7 +3288,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3174,27 +3298,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.170.800-4</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>DERCO S.P.A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>94.141.000-6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3204,13 +3328,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>69425.91</v>
+        <v>1235.95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>654-325-CM26</t>
+          <t>2548-545-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3225,53 +3349,57 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>25882.07</v>
+        <v>44008.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4085-626-CM26</t>
+          <t>4486-282-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3286,7 +3414,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3296,43 +3424,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.170.800-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1213.17</v>
+        <v>69425.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4085-625-CM26</t>
+          <t>654-325-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3352,42 +3484,46 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>60576.41</v>
+        <v>25882.07</v>
       </c>
     </row>
     <row r="49">
@@ -3441,7 +3577,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3454,7 +3594,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2885-435-CM26</t>
+          <t>4085-626-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3479,27 +3619,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3649,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>17016.13</v>
+        <v>1213.17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>655-136-CM26</t>
+          <t>4085-625-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3540,27 +3680,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.821.000-6</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,7 +3710,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>59227.84</v>
+        <v>60576.41</v>
       </c>
     </row>
     <row r="52">
@@ -3624,7 +3764,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3637,7 +3781,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3712-634-CM26</t>
+          <t>2885-435-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3652,7 +3796,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3662,43 +3806,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>36228.27</v>
+        <v>17016.13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29-1925-CM26</t>
+          <t>655-136-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3713,7 +3861,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3723,27 +3871,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.821.000-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3753,13 +3901,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>74255.63</v>
+        <v>59227.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1284047-51-CM26</t>
+          <t>3712-634-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3784,43 +3932,47 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.057.349-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27534.66</v>
+        <v>36228.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1284047-52-CM26</t>
+          <t>29-1925-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3845,43 +3997,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>65.057.349-8</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1582.54</v>
+        <v>74255.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3232-662-CM26</t>
+          <t>1284047-51-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3906,43 +4062,47 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>65.057.349-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>39349.29</v>
+        <v>27534.66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1738-372-CM26</t>
+          <t>1284047-52-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3967,43 +4127,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>65.057.349-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25888.05</v>
+        <v>1582.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2694-228-CM26</t>
+          <t>3232-662-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4018,7 +4182,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4028,12 +4192,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4051,20 +4215,24 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>34300.29</v>
+        <v>39349.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4170-270-CM26</t>
+          <t>1738-372-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4079,7 +4247,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4089,32 +4257,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4123,7 +4291,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>94828.49000000001</v>
+        <v>25888.05</v>
       </c>
     </row>
     <row r="61">
@@ -4177,7 +4345,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4238,7 +4410,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4299,7 +4475,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4312,7 +4492,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1596-228-CM26</t>
+          <t>4170-270-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4327,7 +4507,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4337,32 +4517,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4371,13 +4551,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>122392.49</v>
+        <v>94828.49000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3181-417-CM26</t>
+          <t>2694-228-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4392,7 +4572,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4402,43 +4582,47 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>30208.85</v>
+        <v>34300.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1098710-337-CM26</t>
+          <t>1596-228-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4453,7 +4637,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4463,43 +4647,47 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>53677.64</v>
+        <v>122392.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>528208-102-CM26</t>
+          <t>528208-103-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4547,20 +4735,24 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>26530.31</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>528208-103-CM26</t>
+          <t>3181-417-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4585,97 +4777,235 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>KOVACS SPA</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>639.99</v>
+        <v>30208.85</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>1098710-337-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>62.000.740-4</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>53677.64</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>528208-102-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.254.200-2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>26530.31</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>3181-418-CM26</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>69.080.200-7</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
         <v>445.69</v>
       </c>
     </row>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/sep-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/sep-2026.xlsx
@@ -814,7 +814,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/sep-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>585-115-CM26</t>
+          <t>5158-100-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1046,37 +1046,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>25127.36</v>
+        <v>147977.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>585-114-CM26</t>
+          <t>4168-1233-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1111,37 +1111,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26219.86</v>
+        <v>53039.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>585-113-CM26</t>
+          <t>5158-111-SE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1176,37 +1176,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>25127.36</v>
+        <v>87066.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5158-100-CM26</t>
+          <t>5158-112-SE26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>147977.08</v>
+        <v>29663.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5158-111-SE26</t>
+          <t>585-113-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1306,37 +1306,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>87066.39</v>
+        <v>25127.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4168-1233-CM26</t>
+          <t>585-114-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1376,32 +1376,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>53039.13</v>
+        <v>26219.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4858-804-CM26</t>
+          <t>585-115-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>34871.35</v>
+        <v>25127.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5158-112-SE26</t>
+          <t>4858-804-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1506,32 +1506,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>29663.79</v>
+        <v>34871.35</v>
       </c>
     </row>
     <row r="18">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1223542-174-CM26</t>
+          <t>2859-1011-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1957,47 +1957,43 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.104.928-8</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13638.66</v>
+        <v>71710.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1223542-175-CM26</t>
+          <t>1223542-174-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2056,13 +2052,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>197.3</v>
+        <v>13638.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4036-374-CM26</t>
+          <t>1223542-175-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,43 +2083,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>77.050.575-5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>50760.61</v>
+        <v>197.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2859-1011-CM26</t>
+          <t>4036-374-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>71710.75</v>
+        <v>50760.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>651-153-CM26</t>
+          <t>5612-180-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2204,37 +2204,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2243,13 +2243,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>29827.14</v>
+        <v>39756.82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>651-154-CM26</t>
+          <t>642-179-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.818.000-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>435.68</v>
+        <v>61013.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>642-179-CM26</t>
+          <t>651-153-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2339,27 +2339,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.818.000-K</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>61013.48</v>
+        <v>29827.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5612-180-CM26</t>
+          <t>651-154-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2404,32 +2404,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>39756.82</v>
+        <v>435.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5413-979-CM26</t>
+          <t>2432-632-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>32671.57</v>
+        <v>17061.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2432-632-CM26</t>
+          <t>4803-226-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2534,32 +2534,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>17061.25</v>
+        <v>36732.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4803-226-CM26</t>
+          <t>29-1907-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2599,32 +2599,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>36732.47</v>
+        <v>58176.41</v>
       </c>
     </row>
     <row r="35">
@@ -2704,7 +2704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29-1907-CM26</t>
+          <t>2458-270-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>58176.41</v>
+        <v>22017.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2458-270-CM26</t>
+          <t>4371-409-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2794,41 +2794,37 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>PORTILLO S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.670-1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>22017.08</v>
+        <v>217.61</v>
       </c>
     </row>
     <row r="38">
@@ -2960,7 +2956,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4371-409-CM26</t>
+          <t>1546284-2-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2975,7 +2971,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2985,43 +2981,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PORTILLO S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.008.670-1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>217.61</v>
+        <v>74856.99000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1546284-2-CM26</t>
+          <t>1483311-6-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3046,32 +3046,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>74856.99000000001</v>
+        <v>24520.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1483311-6-CM26</t>
+          <t>1483311-7-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>24520.12</v>
+        <v>1032.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1483311-7-CM26</t>
+          <t>756-289-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3191,32 +3191,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DERCO S.P.A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>94.141.000-6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1032.44</v>
+        <v>38751.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>756-289-CM26</t>
+          <t>756-290-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3271,13 +3267,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>38751.05</v>
+        <v>1235.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>756-290-CM26</t>
+          <t>2548-545-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3292,7 +3288,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3302,43 +3298,47 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DERCO S.P.A</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>94.141.000-6</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1235.95</v>
+        <v>44008.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2548-545-CM26</t>
+          <t>4486-282-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.170.800-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>44008.37</v>
+        <v>69425.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4486-282-CM26</t>
+          <t>654-325-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3418,22 +3418,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.170.800-4</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3462,13 +3462,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>69425.91</v>
+        <v>25882.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>654-325-CM26</t>
+          <t>654-326-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>25882.07</v>
+        <v>411.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>654-326-CM26</t>
+          <t>4085-626-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3553,52 +3553,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>411.49</v>
+        <v>1213.17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4085-626-CM26</t>
+          <t>4085-625-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3653,13 +3649,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1213.17</v>
+        <v>60576.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4085-625-CM26</t>
+          <t>2885-435-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3684,37 +3680,41 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>60576.41</v>
+        <v>17016.13</v>
       </c>
     </row>
     <row r="52">
@@ -3785,7 +3785,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2885-435-CM26</t>
+          <t>655-136-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3810,47 +3810,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>61.821.000-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17016.13</v>
+        <v>59227.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>655-136-CM26</t>
+          <t>625-339-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3875,43 +3871,47 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.821.000-6</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>59227.84</v>
+        <v>37372.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3712-634-CM26</t>
+          <t>1738-372-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3936,32 +3936,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3970,13 +3970,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>36228.27</v>
+        <v>25888.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29-1925-CM26</t>
+          <t>3232-662-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3996,37 +3996,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>74255.63</v>
+        <v>39349.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1284047-51-CM26</t>
+          <t>1284047-52-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>27534.66</v>
+        <v>1582.54</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1284047-52-CM26</t>
+          <t>3712-634-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4126,37 +4126,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65.057.349-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1582.54</v>
+        <v>36228.27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3232-662-CM26</t>
+          <t>29-1925-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4191,37 +4191,37 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4230,13 +4230,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>39349.29</v>
+        <v>74255.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1738-372-CM26</t>
+          <t>1284047-51-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4261,32 +4261,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>65.057.349-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>25888.05</v>
+        <v>27534.66</v>
       </c>
     </row>
     <row r="61">
@@ -4626,7 +4626,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1596-228-CM26</t>
+          <t>2404-1247-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4651,47 +4651,43 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ BALMACEDA LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>86.341.100-9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>122392.49</v>
+        <v>38090.31</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>528208-103-CM26</t>
+          <t>1596-228-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4706,7 +4702,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4716,32 +4712,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4750,13 +4746,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>639.99</v>
+        <v>122392.49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3181-417-CM26</t>
+          <t>528208-103-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4781,27 +4777,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4815,13 +4811,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>30208.85</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1098710-337-CM26</t>
+          <t>3181-417-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4841,32 +4837,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4880,13 +4876,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>53677.64</v>
+        <v>30208.85</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>528208-102-CM26</t>
+          <t>1098710-337-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4911,12 +4907,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4926,12 +4922,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4945,71 +4941,136 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>26530.31</v>
+        <v>53677.64</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>528208-102-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.254.200-2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>26530.31</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>3181-418-CM26</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>69.080.200-7</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
         <v>445.69</v>
       </c>
     </row>
